--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:17</t>
+    <t xml:space="preserve">2026-09-09 22:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:16</t>
+    <t xml:space="preserve">2026-09-17 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>12.52</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>14.36</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="4">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>13.64</v>
+        <v>14.36</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10.47</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8.24</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6.49</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13.39</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>12.52</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12.23</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14.85</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14.36</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13.65</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="11">
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>14.1</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13.64</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13.07</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:43</t>
+    <t xml:space="preserve">2026-09-25 21:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -542,7 +542,7 @@
         <v>-2.54</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-23.03</v>
+        <v>-23.01</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>9</v>
@@ -565,7 +565,7 @@
         <v>-1.88</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-19.07</v>
+        <v>-19.06</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>9</v>
@@ -657,7 +657,7 @@
         <v>-0.87</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6.5</v>
+        <v>-6.51</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>8</v>
@@ -677,10 +677,10 @@
         <v>17.72</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.57</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3.16</v>
+        <v>-3.19</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>7</v>
@@ -703,7 +703,7 @@
         <v>-0.41</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3.65</v>
+        <v>-3.68</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>7</v>
@@ -723,10 +723,10 @@
         <v>14.1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3.26</v>
+        <v>-3.2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>7</v>
@@ -749,7 +749,7 @@
         <v>-0.88</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4.86</v>
+        <v>-4.88</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>6</v>
@@ -769,10 +769,10 @@
         <v>11.79</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.55</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4.58</v>
+        <v>-4.62</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6</v>
@@ -795,7 +795,7 @@
         <v>-0.67</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4.62</v>
+        <v>-4.61</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>6</v>
@@ -818,7 +818,7 @@
         <v>-0.97</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5.02</v>
+        <v>-4.99</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5</v>
@@ -841,7 +841,7 @@
         <v>-0.43</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3.82</v>
+        <v>-3.81</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5</v>
@@ -864,7 +864,7 @@
         <v>-0.63</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4.34</v>
+        <v>-4.31</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
         <v>-0.79</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4.25</v>
+        <v>-4.28</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>4</v>
@@ -910,7 +910,7 @@
         <v>-0.47</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3.99</v>
+        <v>-4.02</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4</v>
@@ -956,7 +956,7 @@
         <v>-0.72</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-3.9</v>
+        <v>-3.89</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>3</v>
@@ -979,7 +979,7 @@
         <v>-0.33</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2.76</v>
+        <v>-2.75</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>3</v>
@@ -999,10 +999,10 @@
         <v>14.85</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-3.3</v>
+        <v>-3.27</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3</v>
@@ -1025,7 +1025,7 @@
         <v>-1.51</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-6.33</v>
+        <v>-6.32</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>2</v>
@@ -1045,10 +1045,10 @@
         <v>12.46</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4.57</v>
+        <v>-4.62</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>2</v>
@@ -1071,7 +1071,7 @@
         <v>-0.92</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-5.36</v>
+        <v>-5.35</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>2</v>
@@ -1094,7 +1094,7 @@
         <v>-0.99</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4.7</v>
+        <v>-4.69</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1</v>
@@ -1114,10 +1114,10 @@
         <v>15.61</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4.87</v>
+        <v>-4.91</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>1</v>
@@ -1140,7 +1140,7 @@
         <v>-0.84</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4.71</v>
+        <v>-4.73</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:39</t>
+    <t xml:space="preserve">2026-10-05 07:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
